--- a/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>45,17</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>40,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>38,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>31,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>117,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,25; 52,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,81; 46,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,99; 45,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,98; 39,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,93; 157,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,37; 113,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,37; 100,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,64; 73,7</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>45,65</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>46,23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>38,72</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>119,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>123,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,87; 51,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,55; 51,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,96; 44,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,49; 25,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,31; 151,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,68; 152,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,58; 101,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,43; 37,24</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>54,66</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>42,18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,88</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>191,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>101,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,11; 61,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,32; 48,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,92; 37,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,73; 18,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>138,72; 251,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,87; 132,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,91; 70,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,51; 25,6</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>52,16</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,77</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>31,18</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>172,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,71; 57,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,37; 41,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,81; 37,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,2; 35,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>129,85; 221,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,78; 94,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,06; 80,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,9; 62,22</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>50,63</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,89</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,73</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>140,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>164,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,32; 58,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,99; 57,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,41; 43,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,69; 12,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>99,82; 193,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>117,09; 241,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,74; 84,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,9; 14,78</t>
         </is>
       </c>
     </row>
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>60,71</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>42,81</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>43,8</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>14,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>226,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,67; 67,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,2; 49,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,32; 50,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,77; 20,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>174,15; 308,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,05; 130,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,38; 130,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,05; 28,1</t>
         </is>
       </c>
     </row>
@@ -1212,42 +1212,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>45,56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,55</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,46</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>111,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,99; 50,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,55; 41,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,57; 38,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,79; 26,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,09; 138,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,38; 98,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,01; 80,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,11; 38,51</t>
         </is>
       </c>
     </row>
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>50,72</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,13</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>29,04</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>61,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>163,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>192,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,4; 55,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,47; 40,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,72; 33,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,89; 78,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>134,45; 195,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,33; 93,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,44; 60,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>110,26; 556,42</t>
         </is>
       </c>
     </row>
@@ -1412,42 +1412,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,87</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,87</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>145,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,7; 51,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,72; 42,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,35; 36,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,81; 42,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133,71; 159,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,41; 99,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,17; 70,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,32; 88,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,56</t>
+          <t>34,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,25; 52,06</t>
+          <t>37,26; 52,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,81; 46,78</t>
+          <t>33,25; 47,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,99; 45,48</t>
+          <t>30,89; 45,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,35</t>
+          <t>27,32; 40,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,93; 157,43</t>
+          <t>84,35; 157,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,37; 113,02</t>
+          <t>65,13; 117,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,37; 100,46</t>
+          <t>54,61; 99,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,64; 73,7</t>
+          <t>43,5; 76,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,97</t>
+          <t>17,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,87; 51,12</t>
+          <t>40,19; 50,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,55; 51,51</t>
+          <t>40,38; 51,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,96; 44,15</t>
+          <t>32,94; 44,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 25,06</t>
+          <t>11,8; 24,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,31; 151,28</t>
+          <t>96,47; 150,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,68; 152,27</t>
+          <t>96,34; 152,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,58; 101,66</t>
+          <t>63,71; 101,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 37,24</t>
+          <t>15,01; 35,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>13,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,11; 61,0</t>
+          <t>48,17; 60,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 48,66</t>
+          <t>35,3; 48,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 37,53</t>
+          <t>24,64; 37,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 18,58</t>
+          <t>8,31; 19,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>138,72; 251,27</t>
+          <t>145,6; 254,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,87; 132,44</t>
+          <t>76,94; 135,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,91; 70,08</t>
+          <t>39,68; 68,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 25,6</t>
+          <t>10,54; 27,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,55</t>
+          <t>23,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,71; 57,86</t>
+          <t>45,53; 57,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,37; 41,23</t>
+          <t>28,07; 41,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,81; 37,61</t>
+          <t>24,37; 37,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 35,52</t>
+          <t>15,87; 31,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>129,85; 221,31</t>
+          <t>130,26; 226,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,78; 94,09</t>
+          <t>52,21; 94,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,06; 80,99</t>
+          <t>43,54; 80,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 62,22</t>
+          <t>22,92; 53,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,32; 58,64</t>
+          <t>42,49; 59,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,99; 57,87</t>
+          <t>40,96; 57,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 43,18</t>
+          <t>27,6; 42,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,56</t>
+          <t>1,51; 10,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>99,82; 193,35</t>
+          <t>100,98; 204,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>117,09; 241,09</t>
+          <t>112,23; 234,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,74; 84,25</t>
+          <t>43,47; 83,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 14,78</t>
+          <t>1,88; 13,1</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,67; 67,18</t>
+          <t>53,1; 66,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,2; 49,5</t>
+          <t>35,44; 50,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,32; 50,22</t>
+          <t>35,88; 50,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,36</t>
+          <t>9,16; 20,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>174,15; 308,82</t>
+          <t>170,03; 309,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,05; 130,3</t>
+          <t>72,1; 133,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,38; 130,7</t>
+          <t>71,97; 129,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,05; 28,1</t>
+          <t>11,36; 28,18</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,04</t>
+          <t>15,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,99; 50,84</t>
+          <t>41,03; 50,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,55; 41,66</t>
+          <t>31,78; 41,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 38,83</t>
+          <t>29,43; 39,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,79; 26,28</t>
+          <t>10,32; 19,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,09; 138,3</t>
+          <t>92,81; 135,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,38; 98,08</t>
+          <t>64,57; 99,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,01; 80,18</t>
+          <t>52,75; 81,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,11; 38,51</t>
+          <t>13,6; 28,65</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61,14</t>
+          <t>49,32</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>192,17%</t>
+          <t>113,86%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,4; 55,17</t>
+          <t>45,9; 55,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,47; 40,57</t>
+          <t>31,48; 40,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,72; 33,41</t>
+          <t>24,74; 33,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48,89; 78,68</t>
+          <t>45,16; 53,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>134,45; 195,55</t>
+          <t>134,72; 197,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,33; 93,89</t>
+          <t>62,9; 93,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,44; 60,36</t>
+          <t>40,22; 60,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>110,26; 556,42</t>
+          <t>96,98; 134,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30,24</t>
+          <t>25,16</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,7; 51,97</t>
+          <t>47,68; 52,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,72; 42,01</t>
+          <t>37,79; 42,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,35; 36,43</t>
+          <t>32,19; 36,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,81; 42,85</t>
+          <t>22,8; 27,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>133,71; 159,42</t>
+          <t>132,88; 159,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>83,41; 99,05</t>
+          <t>83,6; 100,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,17; 70,77</t>
+          <t>58,67; 70,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,32; 88,84</t>
+          <t>33,81; 42,74</t>
         </is>
       </c>
     </row>
